--- a/Doo-Doc/Nueva Version Victus/Event Storming/Residentes - Event Storming.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Event Storming/Residentes - Event Storming.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Event Storming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43A37FF-84B9-4B39-8D65-64C1A5F6C61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1603E49-3769-4C21-873F-A2FE737090B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
   </bookViews>
   <sheets>
     <sheet name="Flujo de eventos en el tiempo" sheetId="61" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Inmueble" sheetId="24" r:id="rId3"/>
     <sheet name="Residente" sheetId="69" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Listado Objetos de Dominio'!$A$3:$B$6</definedName>
   </definedNames>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="115">
   <si>
     <t>Descripción</t>
   </si>
@@ -152,12 +155,6 @@
     <t>Modificar administrador</t>
   </si>
   <si>
-    <t>Información del conjunto residencial al cual se va a modificar un administrador</t>
-  </si>
-  <si>
-    <t>Información del conjunto residencial al cual se va a buscar un administrador</t>
-  </si>
-  <si>
     <t>Inmueble</t>
   </si>
   <si>
@@ -176,36 +173,12 @@
     <t>ZonaInmueble</t>
   </si>
   <si>
-    <t>Asegurar que los datos requeridos para registrar la información del nuevo administrador sean válidos a nivel de tipo de dato,formato, rango, longitud y obligatoriedad.</t>
-  </si>
-  <si>
     <t>Objeto de dominio que representa una Zona de Inmuebles en un conjunto residencial se refiere a una agrupación de unidades habitacionales (como una torre, bloque, o lote) que comparten una ubicación física y características comunes dentro del conjunto.</t>
   </si>
   <si>
-    <t>Inmueb-Pol0001</t>
-  </si>
-  <si>
-    <t>Se debe asegurar exista un inmueble.</t>
-  </si>
-  <si>
-    <t>No es posible tener mas de un tipo inmueble que tenga el mismo número de vivienda más la misma zona inmueble.</t>
-  </si>
-  <si>
-    <t>Asegurar que el identificador del imueble que se desea eliminar  no  haya sido asignado previamente a otro conjunto residencial.</t>
-  </si>
-  <si>
     <t>Resid-Pol0001</t>
   </si>
   <si>
-    <t>Inmueb-Pol0002</t>
-  </si>
-  <si>
-    <t>Inmueb-Pol0003</t>
-  </si>
-  <si>
-    <t>Inmueb-Pol0004</t>
-  </si>
-  <si>
     <t>Resid-Pol0002</t>
   </si>
   <si>
@@ -218,19 +191,205 @@
     <t>Asegurar que los datos requeridos para registrar la información del nuevo residente sean válidos a nivel de tipo de dato,formato, rango, longitud y obligatoriedad.</t>
   </si>
   <si>
-    <t>Se debe asegurar que no exista otro Residente registrado con el mismo tipo y numero de documento de identidad.</t>
-  </si>
-  <si>
-    <t>Se debe asegurar que no exista otro Residente registrado con el mismo numero de contacto.</t>
-  </si>
-  <si>
-    <t>Se debe asegurar que no exista otro residente registrado con el mismo correo electronico.</t>
-  </si>
-  <si>
     <t>Resid-Pol0005</t>
   </si>
   <si>
-    <t>Asegurar que el identificador del residente que se desea registrar  no ha haya sido asignado previamente a otro residente.</t>
+    <t>Residente debe estar asociado a un Inmueble existente en el contexto Conjuntos Residenciales</t>
+  </si>
+  <si>
+    <t>Los datos personales del residente deben ser válidos.</t>
+  </si>
+  <si>
+    <t>Se debe asegurar que exista.</t>
+  </si>
+  <si>
+    <t>Los datos personales y la referencia al Inmueble deben ser válidos.</t>
+  </si>
+  <si>
+    <t>Resid-Pol0006</t>
+  </si>
+  <si>
+    <t>Resid-Pol0007</t>
+  </si>
+  <si>
+    <t>Resid-Pol0008</t>
+  </si>
+  <si>
+    <t>El Residente debe existir en el sistema.</t>
+  </si>
+  <si>
+    <t>El Residente debe estar desvinculado de cualquier Inmueble antes de ser eliminado, si aplica la política.</t>
+  </si>
+  <si>
+    <t>Sistema de Registro de Residentes</t>
+  </si>
+  <si>
+    <t>VincularInmueble Residente</t>
+  </si>
+  <si>
+    <t>DesvincularInmueble Residente</t>
+  </si>
+  <si>
+    <t>Resid-Pol0009</t>
+  </si>
+  <si>
+    <t>Resid-Pol00010</t>
+  </si>
+  <si>
+    <t>Resid-Pol00011</t>
+  </si>
+  <si>
+    <t>Resid-Pol00012</t>
+  </si>
+  <si>
+    <t>El Residente y el Inmueble deben existir.</t>
+  </si>
+  <si>
+    <t>El Inmueble debe estar disponible para asignación.</t>
+  </si>
+  <si>
+    <t>El Residente debe tener un Inmueble vinculado.</t>
+  </si>
+  <si>
+    <t>Residente Vinculado</t>
+  </si>
+  <si>
+    <t>Residente Desvinculado</t>
+  </si>
+  <si>
+    <t>Residente registrado</t>
+  </si>
+  <si>
+    <t>Inmueble Registrado</t>
+  </si>
+  <si>
+    <t>Se debe realizar el proceso de actualización de estado en el Inmueble en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Eliminar Residente</t>
+  </si>
+  <si>
+    <t>Eliminar Inmueble</t>
+  </si>
+  <si>
+    <t>Action/Inmmand</t>
+  </si>
+  <si>
+    <t>Inmandos Posteriores</t>
+  </si>
+  <si>
+    <t>Crear Inmueble</t>
+  </si>
+  <si>
+    <t>Acción dónde un administrador podrá crear una Inmueble</t>
+  </si>
+  <si>
+    <t>información Zona Inmueble</t>
+  </si>
+  <si>
+    <t>Información del Zona Inmueble al que se encuentra asociada la Inmueble que se desea crear.</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0001</t>
+  </si>
+  <si>
+    <t>Asegurar que los datos requeridos para registrar la información del nuevo inmueble que sean válidos a nivel de tipo de dato,formato, rango, longitud y obligatoriedad.</t>
+  </si>
+  <si>
+    <t>Inmueble creado</t>
+  </si>
+  <si>
+    <t>Inmueble eliminada</t>
+  </si>
+  <si>
+    <t>Buscar Inmueble</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0002</t>
+  </si>
+  <si>
+    <t>La combinación de TipoInmueble, numeroVivienda y ZonaInmueble debe ser única.</t>
+  </si>
+  <si>
+    <t>Modificar Inmueble</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0003</t>
+  </si>
+  <si>
+    <t>TipoInmueble y ZonaInmueble deben ser referencias válidas.</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buscar inmueble </t>
+  </si>
+  <si>
+    <t>Acción de buscar una Inmueble especifica</t>
+  </si>
+  <si>
+    <t>Información del Zona Inmueble al que se encuentra asociada la Inmueble que se desea buscar.</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0004</t>
+  </si>
+  <si>
+    <t>Asegurar que el identificador del inmueble que se decea buscar exista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inmueble buscado </t>
+  </si>
+  <si>
+    <t>Inmueble creada</t>
+  </si>
+  <si>
+    <t>Acción de modificar los atributos de una Inmueble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inmueble </t>
+  </si>
+  <si>
+    <t>Información del Zona Inmueble al que se encuentra asociada la Inmueble que se desea modificar</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0005</t>
+  </si>
+  <si>
+    <t>Asegurar que el identificador del conjunto residencial que se desea registrar  no ha haya sido asignado previamente a otro conjunto residencial.</t>
+  </si>
+  <si>
+    <t>Inmueble modificado</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0006</t>
+  </si>
+  <si>
+    <t>Si se cambia TipoInmueble, numeroVivienda o ZonaInmueble, la combinación debe seguir siendo única.</t>
+  </si>
+  <si>
+    <t>Acción de eliminar una Inmueble de un Zona Inmueble.</t>
+  </si>
+  <si>
+    <t>Información del Zona Inmueble al que se encuentra asociada la Inmueble que se desea eliminar.</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0007</t>
+  </si>
+  <si>
+    <t>Se debe asegurar exista una zona inmueble.</t>
+  </si>
+  <si>
+    <t>Inmueble eliminado</t>
+  </si>
+  <si>
+    <t>Crear Inmueble.</t>
+  </si>
+  <si>
+    <t>Inmueble-Pol0008</t>
+  </si>
+  <si>
+    <t>El Inmueble no debe estar asignado a ningún residente antes de ser eliminado.</t>
   </si>
 </sst>
 </file>
@@ -290,7 +449,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,8 +558,44 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -413,81 +608,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -536,23 +656,53 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="thick">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
@@ -560,58 +710,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -622,7 +728,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -634,80 +740,113 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -715,101 +854,128 @@
     <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -821,12 +987,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC99FF"/>
       <color rgb="FFC3895D"/>
       <color rgb="FFFA90B1"/>
       <color rgb="FFFDD3FA"/>
       <color rgb="FFFDD3DD"/>
       <color rgb="FFFCFCAA"/>
-      <color rgb="FFCC99FF"/>
       <color rgb="FFC1EE5C"/>
       <color rgb="FFFF0066"/>
       <color rgb="FFCCCC00"/>
@@ -891,6 +1057,43 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Flujo de eventos en el tiempo"/>
+      <sheetName val="Listado Objetos de Dominio"/>
+      <sheetName val="ConjuntoResidencial"/>
+      <sheetName val="ZonaComun"/>
+      <sheetName val="Administrador"/>
+      <sheetName val="ZonaInmueble"/>
+      <sheetName val="Inmueble"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Inmueble</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Objeto de dominio que representa un inmueble dentro de una zona de inmuebles en un conjunto residencial describe las características específicas de una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona de inmueble</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1221,77 +1424,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="2" spans="1:4" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="43" t="str">
         <f>$B$1</f>
         <v>Residentes</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="B5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="44"/>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1311,7 +1514,499 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9732BFC6-5B3A-4E40-BEA3-58E7EDB79B0C}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38" style="1" customWidth="1"/>
+    <col min="13" max="13" width="46.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="132.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="66.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="52.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+    </row>
+    <row r="2" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="53" t="str">
+        <f>'[1]Listado Objetos de Dominio'!A8</f>
+        <v>Inmueble</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="53" t="str">
+        <f>'[1]Listado Objetos de Dominio'!B8</f>
+        <v>Objeto de dominio que representa un inmueble dentro de una zona de inmuebles en un conjunto residencial describe las características específicas de una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona de inmueble</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="55"/>
+      <c r="I4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="55"/>
+      <c r="I5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="56"/>
+      <c r="M5" s="57"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="62"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
+    </row>
+    <row r="7" spans="1:14" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" s="36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" s="49"/>
+      <c r="L10" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="51.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="29"/>
+      <c r="J12" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="29"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" s="29"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="K14" s="23"/>
+      <c r="L14" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="54">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="L10:L13"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{7A665DD2-2C92-423E-A603-0407226FFBD7}"/>
+    <hyperlink ref="A1:N1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{652D2B05-9792-4E6A-86E5-B29B7C50F242}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB74C4-8D06-495C-9F2F-FA132D609BF5}">
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1336,839 +2031,484 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46" t="str">
-        <f>'Listado Objetos de Dominio'!A6</f>
-        <v>Inmueble</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47"/>
+      <c r="B2" s="78" t="str">
+        <f>'Listado Objetos de Dominio'!A4</f>
+        <v>Residente</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="48" t="str">
+      <c r="B3" s="53" t="str">
         <f>'Listado Objetos de Dominio'!B6</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="50"/>
+      <c r="D4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51" t="s">
+      <c r="F4" s="54"/>
+      <c r="G4" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="9" t="s">
+      <c r="H4" s="55"/>
+      <c r="I4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="80" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+    <row r="5" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="54" t="s">
+      <c r="F5" s="54"/>
+      <c r="G5" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="56" t="s">
+      <c r="H5" s="76"/>
+      <c r="I5" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="11" t="s">
+      <c r="L5" s="79"/>
+      <c r="M5" s="80"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="81"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="I6" s="77"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="80"/>
+    </row>
+    <row r="7" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="36" t="str">
-        <f>_xlfn.CONCAT("Registrar ",B2)</f>
-        <v>Registrar Inmueble</v>
-      </c>
-      <c r="C7" s="36" t="str">
-        <f>_xlfn.CONCAT("Acción de registrar un ",B2," para un conjunto residencial.")</f>
-        <v>Acción de registrar un Inmueble para un conjunto residencial.</v>
-      </c>
-      <c r="D7" s="36" t="str">
-        <f>B2</f>
-        <v>Inmueble</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36" t="str">
-        <f>_xlfn.CONCAT(B2," registrado")</f>
-        <v>Inmueble registrado</v>
-      </c>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36" t="str">
-        <f>_xlfn.CONCAT(B2," eliminado")</f>
-        <v>Inmueble eliminado</v>
-      </c>
-      <c r="M7" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="22" t="str">
-        <f>_xlfn.CONCAT("Buscar ",B2)</f>
-        <v>Buscar Inmueble</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="22" t="str">
-        <f>_xlfn.CONCAT("Eliminar ",B2)</f>
-        <v>Eliminar Inmueble</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="24" t="str">
-        <f>_xlfn.CONCAT("Modificar ",B2)</f>
-        <v>Modificar Inmueble</v>
-      </c>
-      <c r="C10" s="24" t="str">
-        <f>_xlfn.CONCAT("Acción de modificar la información asociada a un ",B2," del conjunto residencial.")</f>
-        <v>Acción de modificar la información asociada a un Inmueble del conjunto residencial.</v>
-      </c>
-      <c r="D10" s="24" t="str">
-        <f>B2</f>
-        <v>Inmueble</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24" t="str">
-        <f>_xlfn.CONCAT(B2," modificado")</f>
-        <v>Inmueble modificado</v>
-      </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="39" t="str">
-        <f>_xlfn.CONCAT(B2," registrado")</f>
-        <v>Inmueble registrado</v>
-      </c>
-      <c r="M10" s="22" t="str">
-        <f>_xlfn.CONCAT("Eliminar ",$B$2)</f>
-        <v>Eliminar Inmueble</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="36" t="str">
-        <f>_xlfn.CONCAT("Buscar ",B2)</f>
-        <v>Buscar Inmueble</v>
-      </c>
-      <c r="C11" s="36" t="str">
-        <f>_xlfn.CONCAT("Acción de buscar la información asociada a un ",B2," del conjunto residencial.")</f>
-        <v>Acción de buscar la información asociada a un Inmueble del conjunto residencial.</v>
-      </c>
-      <c r="D11" s="36" t="str">
-        <f>B2</f>
-        <v>Inmueble</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36" t="str">
-        <f>_xlfn.CONCAT(B2," buscado")</f>
-        <v>Inmueble buscado</v>
-      </c>
-      <c r="K11" s="36"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="22" t="str">
-        <f>_xlfn.CONCAT("Modificar ",$B$2)</f>
-        <v>Modificar Inmueble</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="26" t="str">
-        <f>_xlfn.CONCAT("Eliminar ",$B$2)</f>
-        <v>Eliminar Inmueble</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="24" t="str">
-        <f>_xlfn.CONCAT("Dar de baja ",B2)</f>
-        <v>Dar de baja Inmueble</v>
-      </c>
-      <c r="C13" s="24" t="str">
-        <f>_xlfn.CONCAT("Acción de eliminar a un ",B2," de un conjunto residencial.")</f>
-        <v>Acción de eliminar a un Inmueble de un conjunto residencial.</v>
-      </c>
-      <c r="D13" s="24" t="str">
-        <f>B2</f>
-        <v>Inmueble</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24" t="str">
-        <f>_xlfn.CONCAT(B2," eliminado")</f>
-        <v>Inmueble eliminado</v>
-      </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="22" t="str">
-        <f>_xlfn.CONCAT("Crear ",$B$2)</f>
-        <v>Crear Inmueble</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E14" s="27"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L10:L13"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{171D8416-5555-47CC-88C6-059E12392622}"/>
-    <hyperlink ref="A1:N1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{AE348A16-53E2-4CCC-93B2-754A740B8500}"/>
-    <hyperlink ref="D1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{8470BA21-67E5-43CC-8F2E-84E0BD40E9C4}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB74C4-8D06-495C-9F2F-FA132D609BF5}">
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="18.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="43.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38" style="1" customWidth="1"/>
-    <col min="13" max="13" width="46.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="132.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="50.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="66.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="52.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="46" t="str">
-        <f>'Listado Objetos de Dominio'!A4</f>
-        <v>Residente</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="48" t="str">
-        <f>'Listado Objetos de Dominio'!B6</f>
-        <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="36" t="str">
+      <c r="B7" s="75" t="str">
         <f>_xlfn.CONCAT("Registrar ",B2)</f>
         <v>Registrar Residente</v>
       </c>
-      <c r="C7" s="36" t="str">
+      <c r="C7" s="75" t="str">
         <f>_xlfn.CONCAT("Acción de registrar un ",B2," para un conjunto residencial.")</f>
         <v>Acción de registrar un Residente para un conjunto residencial.</v>
       </c>
-      <c r="D7" s="36" t="str">
+      <c r="D7" s="47" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36" t="str">
+      <c r="G7" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="75"/>
+      <c r="J7" s="48" t="str">
         <f>_xlfn.CONCAT(B2," registrado")</f>
         <v>Residente registrado</v>
       </c>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36" t="str">
+      <c r="K7" s="75"/>
+      <c r="L7" s="48" t="str">
         <f>_xlfn.CONCAT(B2," eliminado")</f>
         <v>Residente eliminado</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="22" t="str">
+    <row r="8" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="75"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="23" t="str">
         <f>_xlfn.CONCAT("Buscar ",B2)</f>
         <v>Buscar Residente</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="22" t="str">
+    <row r="9" spans="1:14" ht="58.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="73"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="75"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="23" t="str">
         <f>_xlfn.CONCAT("Eliminar ",B2)</f>
         <v>Eliminar Residente</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="24" t="str">
+    <row r="10" spans="1:14" ht="90" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
+      <c r="B10" s="71" t="str">
         <f>_xlfn.CONCAT("Modificar ",B2)</f>
         <v>Modificar Residente</v>
       </c>
-      <c r="C10" s="24" t="str">
+      <c r="C10" s="71" t="str">
         <f>_xlfn.CONCAT("Acción de modificar la información asociada a un ",B2," del conjunto residencial.")</f>
         <v>Acción de modificar la información asociada a un Residente del conjunto residencial.</v>
       </c>
-      <c r="D10" s="24" t="str">
-        <f>B2</f>
-        <v>Residente</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24" t="str">
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="71" t="str">
         <f>_xlfn.CONCAT(B2," modificado")</f>
         <v>Residente modificado</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="39" t="str">
+      <c r="K10" s="25"/>
+      <c r="L10" s="47" t="str">
         <f>_xlfn.CONCAT(B2," registrado")</f>
         <v>Residente registrado</v>
       </c>
-      <c r="M10" s="22" t="str">
+      <c r="M10" s="65" t="str">
         <f>_xlfn.CONCAT("Eliminar ",$B$2)</f>
         <v>Eliminar Residente</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="36" t="str">
+    <row r="11" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="73"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="66"/>
+    </row>
+    <row r="12" spans="1:14" ht="108" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="73"/>
+      <c r="B12" s="26" t="str">
         <f>_xlfn.CONCAT("Buscar ",B2)</f>
         <v>Buscar Residente</v>
       </c>
-      <c r="C11" s="36" t="str">
+      <c r="C12" s="26" t="str">
         <f>_xlfn.CONCAT("Acción de buscar la información asociada a un ",B2," del conjunto residencial.")</f>
         <v>Acción de buscar la información asociada a un Residente del conjunto residencial.</v>
       </c>
-      <c r="D11" s="36" t="str">
-        <f>B2</f>
-        <v>Residente</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36" t="str">
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="28" t="str">
         <f>_xlfn.CONCAT(B2," buscado")</f>
         <v>Residente buscado</v>
       </c>
-      <c r="K11" s="36"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="22" t="str">
+      <c r="K12" s="26"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="26" t="str">
         <f>_xlfn.CONCAT("Modificar ",$B$2)</f>
         <v>Modificar Residente</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="62"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="26" t="str">
-        <f>_xlfn.CONCAT("Eliminar ",$B$2)</f>
+    <row r="13" spans="1:14" ht="75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="73"/>
+      <c r="B13" s="46" t="str">
+        <f>_xlfn.CONCAT("Eliminar ",B2)</f>
         <v>Eliminar Residente</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="24" t="str">
-        <f>_xlfn.CONCAT("Dar de baja ",B2)</f>
-        <v>Dar de baja Residente</v>
-      </c>
-      <c r="C13" s="24" t="str">
+      <c r="C13" s="46" t="str">
         <f>_xlfn.CONCAT("Acción de eliminar a un ",B2," de un conjunto residencial.")</f>
         <v>Acción de eliminar a un Residente de un conjunto residencial.</v>
       </c>
-      <c r="D13" s="24" t="str">
-        <f>B2</f>
-        <v>Residente</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24" t="str">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="29"/>
+      <c r="J13" s="46" t="str">
         <f>_xlfn.CONCAT(B2," eliminado")</f>
         <v>Residente eliminado</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="22" t="str">
+      <c r="K13" s="29"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="67" t="str">
         <f>_xlfn.CONCAT("Crear ",$B$2)</f>
         <v>Crear Residente</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E14" s="27"/>
-    </row>
+    <row r="14" spans="1:14" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="74"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="30"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="68"/>
+    </row>
+    <row r="15" spans="1:14" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="69" t="str">
+        <f>_xlfn.CONCAT("Acción de vinvular a un ",B2," de un conjunto residencial.")</f>
+        <v>Acción de vinvular a un Residente de un conjunto residencial.</v>
+      </c>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="32"/>
+      <c r="J15" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15" s="63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="32"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="63"/>
+    </row>
+    <row r="17" spans="1:13" ht="49.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47"/>
+      <c r="B17" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="70" t="str">
+        <f>_xlfn.CONCAT("Acción de desvincular a un ",B2," de un conjunto residencial.")</f>
+        <v>Acción de desvincular a un Residente de un conjunto residencial.</v>
+      </c>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="34"/>
+      <c r="L17" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="M17" s="34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="76.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="45">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
@@ -2181,33 +2521,39 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="L7:L9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="J7:J9"/>
     <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="L10:L13"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D7:D18"/>
+    <mergeCell ref="E7:E18"/>
+    <mergeCell ref="F7:F18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="L10:L14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J13:J14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{42C7641C-3E53-48C3-9D18-BDDC9B9DD3BA}"/>

--- a/Doo-Doc/Nueva Version Victus/Event Storming/Residentes - Event Storming.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Event Storming/Residentes - Event Storming.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Event Storming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1603E49-3769-4C21-873F-A2FE737090B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F46C777-2B02-410E-99FE-70395441965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
+    <workbookView xWindow="20250" yWindow="1110" windowWidth="17850" windowHeight="17565" activeTab="2" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
   </bookViews>
   <sheets>
     <sheet name="Flujo de eventos en el tiempo" sheetId="61" r:id="rId1"/>
@@ -863,55 +863,100 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -931,51 +976,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1540,84 +1540,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
     </row>
     <row r="2" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="53" t="str">
+      <c r="B2" s="47" t="str">
         <f>'[1]Listado Objetos de Dominio'!A8</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53" t="str">
+      <c r="B3" s="47" t="str">
         <f>'[1]Listado Objetos de Dominio'!B8</f>
         <v>Objeto de dominio que representa un inmueble dentro de una zona de inmuebles en un conjunto residencial describe las características específicas de una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona de inmueble</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="4"/>
     </row>
     <row r="4" spans="1:14" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="50"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55" t="s">
+      <c r="F4" s="49"/>
+      <c r="G4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="55"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="18" t="s">
         <v>14</v>
       </c>
@@ -1627,52 +1627,52 @@
       <c r="K4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="56" t="s">
+      <c r="L4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="57" t="s">
+      <c r="M4" s="52" t="s">
         <v>76</v>
       </c>
       <c r="N4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="59" t="s">
+      <c r="H5" s="50"/>
+      <c r="I5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="60" t="s">
+      <c r="J5" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="58" t="s">
+      <c r="K5" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="56"/>
-      <c r="M5" s="57"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="52"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="61"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="16" t="s">
         <v>21</v>
       </c>
@@ -1685,29 +1685,29 @@
       <c r="H6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="57"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="52"/>
     </row>
     <row r="7" spans="1:14" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="58" t="s">
         <v>80</v>
       </c>
       <c r="G7" s="37" t="s">
@@ -1716,12 +1716,12 @@
       <c r="H7" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51" t="s">
+      <c r="I7" s="58"/>
+      <c r="J7" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51" t="s">
+      <c r="K7" s="58"/>
+      <c r="L7" s="58" t="s">
         <v>84</v>
       </c>
       <c r="M7" s="36" t="s">
@@ -1729,43 +1729,43 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
       <c r="G8" s="37" t="s">
         <v>86</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
       <c r="M8" s="36" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
       <c r="G9" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H9" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
       <c r="M9" s="36" t="s">
         <v>74</v>
       </c>
@@ -1774,33 +1774,33 @@
       <c r="A10" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49" t="s">
+      <c r="I10" s="60"/>
+      <c r="J10" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="K10" s="49"/>
-      <c r="L10" s="47" t="s">
+      <c r="K10" s="60"/>
+      <c r="L10" s="59" t="s">
         <v>98</v>
       </c>
       <c r="M10" s="22" t="s">
@@ -1811,38 +1811,38 @@
       <c r="A11" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="47"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="59"/>
       <c r="M11" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="61" t="s">
         <v>101</v>
       </c>
       <c r="G12" s="29" t="s">
@@ -1852,22 +1852,22 @@
         <v>103</v>
       </c>
       <c r="I12" s="29"/>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="61" t="s">
         <v>104</v>
       </c>
       <c r="K12" s="29"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47" t="s">
+      <c r="L12" s="59"/>
+      <c r="M12" s="59" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="29" t="s">
         <v>105</v>
       </c>
@@ -1875,28 +1875,28 @@
         <v>106</v>
       </c>
       <c r="I13" s="29"/>
-      <c r="J13" s="46"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="29"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
     </row>
     <row r="14" spans="1:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="62" t="s">
         <v>108</v>
       </c>
       <c r="G14" s="23" t="s">
@@ -1906,11 +1906,11 @@
         <v>110</v>
       </c>
       <c r="I14" s="23"/>
-      <c r="J14" s="48" t="s">
+      <c r="J14" s="62" t="s">
         <v>111</v>
       </c>
       <c r="K14" s="23"/>
-      <c r="L14" s="48" t="s">
+      <c r="L14" s="62" t="s">
         <v>98</v>
       </c>
       <c r="M14" s="23" t="s">
@@ -1918,12 +1918,12 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
       <c r="G15" s="23" t="s">
         <v>113</v>
       </c>
@@ -1931,9 +1931,9 @@
         <v>114</v>
       </c>
       <c r="I15" s="23"/>
-      <c r="J15" s="48"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="23"/>
-      <c r="L15" s="48"/>
+      <c r="L15" s="62"/>
       <c r="M15" s="23" t="s">
         <v>112</v>
       </c>
@@ -1941,6 +1941,44 @@
     <row r="16" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="L10:L13"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
@@ -1957,44 +1995,6 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="L10:L13"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{7A665DD2-2C92-423E-A603-0407226FFBD7}"/>
@@ -2031,84 +2031,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="78" t="str">
+      <c r="B2" s="63" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53" t="str">
+      <c r="B3" s="47" t="str">
         <f>'Listado Objetos de Dominio'!B6</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="4"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="50"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55" t="s">
+      <c r="F4" s="49"/>
+      <c r="G4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="55"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="18" t="s">
         <v>14</v>
       </c>
@@ -2118,52 +2118,52 @@
       <c r="K4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="80" t="s">
+      <c r="M4" s="65" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="76" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="77" t="s">
+      <c r="H5" s="70"/>
+      <c r="I5" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="83" t="s">
+      <c r="J5" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="82" t="s">
+      <c r="K5" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="79"/>
-      <c r="M5" s="80"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="65"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="81"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="61"/>
+      <c r="A6" s="66"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="16" t="s">
         <v>21</v>
       </c>
@@ -2176,32 +2176,32 @@
       <c r="H6" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="I6" s="77"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="80"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="65"/>
     </row>
     <row r="7" spans="1:14" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="75" t="str">
+      <c r="B7" s="69" t="str">
         <f>_xlfn.CONCAT("Registrar ",B2)</f>
         <v>Registrar Residente</v>
       </c>
-      <c r="C7" s="75" t="str">
+      <c r="C7" s="69" t="str">
         <f>_xlfn.CONCAT("Acción de registrar un ",B2," para un conjunto residencial.")</f>
         <v>Acción de registrar un Residente para un conjunto residencial.</v>
       </c>
-      <c r="D7" s="47" t="str">
+      <c r="D7" s="59" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="59" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="24" t="s">
@@ -2210,13 +2210,13 @@
       <c r="H7" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="75"/>
-      <c r="J7" s="48" t="str">
+      <c r="I7" s="69"/>
+      <c r="J7" s="62" t="str">
         <f>_xlfn.CONCAT(B2," registrado")</f>
         <v>Residente registrado</v>
       </c>
-      <c r="K7" s="75"/>
-      <c r="L7" s="48" t="str">
+      <c r="K7" s="69"/>
+      <c r="L7" s="62" t="str">
         <f>_xlfn.CONCAT(B2," eliminado")</f>
         <v>Residente eliminado</v>
       </c>
@@ -2226,21 +2226,21 @@
     </row>
     <row r="8" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="73"/>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
       <c r="G8" s="24" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="75"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="48"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="62"/>
       <c r="M8" s="23" t="str">
         <f>_xlfn.CONCAT("Buscar ",B2)</f>
         <v>Buscar Residente</v>
@@ -2248,21 +2248,21 @@
     </row>
     <row r="9" spans="1:14" ht="58.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="73"/>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="24" t="s">
         <v>45</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="75"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="48"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="62"/>
       <c r="M9" s="23" t="str">
         <f>_xlfn.CONCAT("Eliminar ",B2)</f>
         <v>Eliminar Residente</v>
@@ -2270,17 +2270,17 @@
     </row>
     <row r="10" spans="1:14" ht="90" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="73"/>
-      <c r="B10" s="71" t="str">
+      <c r="B10" s="75" t="str">
         <f>_xlfn.CONCAT("Modificar ",B2)</f>
         <v>Modificar Residente</v>
       </c>
-      <c r="C10" s="71" t="str">
+      <c r="C10" s="75" t="str">
         <f>_xlfn.CONCAT("Acción de modificar la información asociada a un ",B2," del conjunto residencial.")</f>
         <v>Acción de modificar la información asociada a un Residente del conjunto residencial.</v>
       </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
       <c r="G10" s="25" t="s">
         <v>46</v>
       </c>
@@ -2288,27 +2288,27 @@
         <v>51</v>
       </c>
       <c r="I10" s="25"/>
-      <c r="J10" s="71" t="str">
+      <c r="J10" s="75" t="str">
         <f>_xlfn.CONCAT(B2," modificado")</f>
         <v>Residente modificado</v>
       </c>
       <c r="K10" s="25"/>
-      <c r="L10" s="47" t="str">
+      <c r="L10" s="59" t="str">
         <f>_xlfn.CONCAT(B2," registrado")</f>
         <v>Residente registrado</v>
       </c>
-      <c r="M10" s="65" t="str">
+      <c r="M10" s="80" t="str">
         <f>_xlfn.CONCAT("Eliminar ",$B$2)</f>
         <v>Eliminar Residente</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="73"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="25" t="s">
         <v>48</v>
       </c>
@@ -2316,10 +2316,10 @@
         <v>52</v>
       </c>
       <c r="I11" s="25"/>
-      <c r="J11" s="71"/>
+      <c r="J11" s="75"/>
       <c r="K11" s="25"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="66"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="81"/>
     </row>
     <row r="12" spans="1:14" ht="108" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="73"/>
@@ -2331,9 +2331,9 @@
         <f>_xlfn.CONCAT("Acción de buscar la información asociada a un ",B2," del conjunto residencial.")</f>
         <v>Acción de buscar la información asociada a un Residente del conjunto residencial.</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
       <c r="G12" s="27" t="s">
         <v>53</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>Residente buscado</v>
       </c>
       <c r="K12" s="26"/>
-      <c r="L12" s="47"/>
+      <c r="L12" s="59"/>
       <c r="M12" s="26" t="str">
         <f>_xlfn.CONCAT("Modificar ",$B$2)</f>
         <v>Modificar Residente</v>
@@ -2354,17 +2354,17 @@
     </row>
     <row r="13" spans="1:14" ht="75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="73"/>
-      <c r="B13" s="46" t="str">
+      <c r="B13" s="61" t="str">
         <f>_xlfn.CONCAT("Eliminar ",B2)</f>
         <v>Eliminar Residente</v>
       </c>
-      <c r="C13" s="46" t="str">
+      <c r="C13" s="61" t="str">
         <f>_xlfn.CONCAT("Acción de eliminar a un ",B2," de un conjunto residencial.")</f>
         <v>Acción de eliminar a un Residente de un conjunto residencial.</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
       <c r="G13" s="29" t="s">
         <v>54</v>
       </c>
@@ -2372,24 +2372,24 @@
         <v>56</v>
       </c>
       <c r="I13" s="29"/>
-      <c r="J13" s="46" t="str">
+      <c r="J13" s="61" t="str">
         <f>_xlfn.CONCAT(B2," eliminado")</f>
         <v>Residente eliminado</v>
       </c>
       <c r="K13" s="29"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="67" t="str">
+      <c r="L13" s="59"/>
+      <c r="M13" s="82" t="str">
         <f>_xlfn.CONCAT("Crear ",$B$2)</f>
         <v>Crear Residente</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="74"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="30" t="s">
         <v>55</v>
       </c>
@@ -2397,25 +2397,25 @@
         <v>57</v>
       </c>
       <c r="I14" s="30"/>
-      <c r="J14" s="46"/>
+      <c r="J14" s="61"/>
       <c r="K14" s="30"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="68"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="83"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="69" t="str">
+      <c r="C15" s="76" t="str">
         <f>_xlfn.CONCAT("Acción de vinvular a un ",B2," de un conjunto residencial.")</f>
         <v>Acción de vinvular a un Residente de un conjunto residencial.</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
       <c r="G15" s="32" t="s">
         <v>61</v>
       </c>
@@ -2423,24 +2423,24 @@
         <v>65</v>
       </c>
       <c r="I15" s="32"/>
-      <c r="J15" s="63" t="s">
+      <c r="J15" s="78" t="s">
         <v>68</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="M15" s="63" t="s">
+      <c r="M15" s="78" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
       <c r="G16" s="32" t="s">
         <v>62</v>
       </c>
@@ -2448,25 +2448,25 @@
         <v>66</v>
       </c>
       <c r="I16" s="32"/>
-      <c r="J16" s="63"/>
+      <c r="J16" s="78"/>
       <c r="K16" s="32"/>
       <c r="L16" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="63"/>
+      <c r="M16" s="78"/>
     </row>
     <row r="17" spans="1:13" ht="49.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47"/>
-      <c r="B17" s="70" t="s">
+      <c r="A17" s="59"/>
+      <c r="B17" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="70" t="str">
+      <c r="C17" s="77" t="str">
         <f>_xlfn.CONCAT("Acción de desvincular a un ",B2," de un conjunto residencial.")</f>
         <v>Acción de desvincular a un Residente de un conjunto residencial.</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
       <c r="G17" s="34" t="s">
         <v>63</v>
       </c>
@@ -2474,11 +2474,11 @@
         <v>67</v>
       </c>
       <c r="I17" s="34"/>
-      <c r="J17" s="64" t="s">
+      <c r="J17" s="79" t="s">
         <v>69</v>
       </c>
       <c r="K17" s="34"/>
-      <c r="L17" s="64" t="s">
+      <c r="L17" s="79" t="s">
         <v>68</v>
       </c>
       <c r="M17" s="34" t="s">
@@ -2486,12 +2486,12 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="76.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="34" t="s">
         <v>64</v>
       </c>
@@ -2499,9 +2499,9 @@
         <v>72</v>
       </c>
       <c r="I18" s="34"/>
-      <c r="J18" s="64"/>
+      <c r="J18" s="79"/>
       <c r="K18" s="34"/>
-      <c r="L18" s="64"/>
+      <c r="L18" s="79"/>
       <c r="M18" s="34" t="s">
         <v>74</v>
       </c>
@@ -2509,26 +2509,15 @@
     <row r="19" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="L10:L14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J13:J14"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
@@ -2545,15 +2534,26 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="A15:A18"/>
-    <mergeCell ref="L10:L14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="J5:J6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{42C7641C-3E53-48C3-9D18-BDDC9B9DD3BA}"/>
@@ -2565,6 +2565,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C279D002CEC08F42B7087C30E58D0266" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e5713f579c7011938dc4987ae8981b8f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3219184d-29ab-4105-b29c-8e343e335d59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae0a0ff84a3c6712467f60982d6e378d" ns2:_="">
     <xsd:import namespace="3219184d-29ab-4105-b29c-8e343e335d59"/>
@@ -2708,35 +2723,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AEECCE0-61F9-4782-94C5-382F8EFF459D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6724C681-8A04-4D66-BB1C-57F7466573C0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3219184d-29ab-4105-b29c-8e343e335d59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2759,9 +2749,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6724C681-8A04-4D66-BB1C-57F7466573C0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AEECCE0-61F9-4782-94C5-382F8EFF459D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3219184d-29ab-4105-b29c-8e343e335d59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
